--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -2691,11 +2691,6 @@
           <t>2026-07-31 16:11:14</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
           <t>DOYLESTOWN, PA — Drivers should prepare for months of daytime and overnight road closures in downtown Doylestown as PECO Energy begins utility construction affecting sections of State Street and Main Street. Crews will close and detour one section of roadway at a time to minimize disruptions.</t>
@@ -2710,6 +2705,195 @@
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Downtown Travel News</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22Downtown+Travel%22+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://news4sanantonio.com/safedriving/via-rapid-green-line-aims-to-transform-downtown-travel</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-09-16 22:09:27</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Downtown Travel</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Downtown Travel (Brand)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>VIA Rapid Green Line Aims to Transform Downtown Travel - WOAI</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>San Antonio Living</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>by San Antonio Living
+VIA Metropolitan Transit
+Whether you're heading to the airport, downtown, or the missions, the Rapid Green Line could eventually make the trip smoother. Corderro checked in with VIA officials to see where the project stands and what riders can expect once construction is complete.
+The Rapid Green Line is set to become VIA's fastest bus service, connecting key destinations throughout San Antonio while providing a more reliable alternative to driving. Construction is currently underway along San Pedro Avenue, where crews are building improvements designed to keep buses moving efficiently through some of the city's busiest corridors.
+Once completed, buses will travel in dedicated lanes, reducing delays caused by traffic. Service is expected to run every 10 minutes during peak periods, and traffic signal priority technology will help buses move through intersections more quickly. Riders will also be able to pay their fare before boarding, cutting down on time spent at stops and helping the system stay on schedule.
+VIA officials say these upgrades are intended to make public transportation faster, more convenient, and more accessible for residents and visitors alike. The project is expected to provide a smoother ride across downtown while improving connections to some of San Antonio's most popular destinations.
+As construction continues, officials encourage residents to stay informed about traffic impacts and project updates as the city moves closer to launching the new service.
+VIA Metropolitan Transit123 N. MedinaSan Antonio, TX 78207210-362-2020KEEPSAMOVING.COM/CONSTRUCTIONfacebook and twitter: @viatransit</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:44:48</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>by San Antonio Living VIA Metropolitan Transit Whether you're heading to the airport, downtown, or the missions, the Rapid Green Line could eventually make the trip smoother. Corderro checked in with VIA officials to see where the project stands and what riders can expect once construction is complete.</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Downtown Travel News</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22Downtown+Travel%22+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.nomadlawyer.org/providence-pvdfest-cultural-travel-guide-2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-09-16 23:33:34</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Downtown Travel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Downtown Travel (Brand)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Providence PVDFest 2026: Music, Art &amp; Downtown Travel Guide - Nomad Lawyer</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Nomad Lawyer</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Downtown Providence turns its historic core and civic plazas into an open-access cultural celebration during PVDFest 2026.
+While Rhode Island ranks as the smallest state in the American union, its capital city unleashes an outsized cultural celebration where historic red-brick thoroughfares transform into an entirely walkable, vehicle-free urban amphitheater without a single ticket gate. On September 18 and 19, PVDFest 2026 takes over Downtown Providence, dismantling traditional concert hall walls across civic parks, transit plazas, and historic avenues to stage two days of global polyrhythms, indigenous ancestral ceremonies, high-energy brass, and public street art. Rather than confining performances to a cordoned stadium or costly arena, the festival converts the civic core into an open-access cultural playground where neighborhood residents, RISD art students, and international travelers mingle freely among food carts, maker pavilions, and open-air soundstages.
+The celebration runs from 5pm to 10pm on Friday, September 18, and continues from noon to 10pm on Saturday, September 19. By stretching across Burnside Park, Kennedy Plaza, the Providence Rink, Washington Street, Mathewson Street, and Snow Street, the event design encourages visitors to roam unhurried through Downcity Providence. Instead of facing rigid queues or static stadium seating, attendees stroll down cobblestone side streets, discovering brass bands performing on street corners, live painters finishing large-format murals, and impromptu salsa circles springing up on open asphalt.
+The heart of PVDFest 2026 lies in its refusal to compartmentalize genres or segregate performance styles. The festival footprint integrates several civic landmarks, centering its major stage production in Kennedy Plaza while weaving intimate acoustic pockets through nearby avenues. Friday evening begins at 5pm with the debut of the free LUV U BETTER Block Party at the Providence Rink, running straight through to 10pm. This dedicated outdoor session infuses the city center with classic R&amp;B, deep soul, club dance rhythms, and golden-era hip-hop, anchored by regional DJs and vocalists who set an infectious neighborhood tone for the weekend.
+Simultaneously, Friday's live music programming introduces an international auditory range across the surrounding downtown stages. Audiences can transition from the melodic Afrobeat rhythms of Grace Darko to the fiery traditional trumpets of Ashley Soto with Mariachi Tequila, followed by the West African sabar drumming of Lamine Touré and Group Saloum. The Friday lineup also highlights Séga Genn and the hard-hitting dura salsa arrangements of La Excelencia, turning municipal sidewalks into dance floors before the opening night wraps up at 10pm.
+Saturday expands the auditory scope from noon onward, leading toward an electric climax at 8:30pm when New Orleans bounce royalty Big Freedia takes over the Plaza Stage. In a signature showcase of community collaboration organized in tandem with the City of Providence, Big Freedia will perform alongside the Earl Bright &amp; Elevated Choir, fusing high-tempo southern bounce beats with the soaring vocal power of Rhode Island's gospel tradition. Saturday's daylight and dusk schedules feature a diverse cast including soul luminary Butch Tavares, celebrated Malian djembe master Sidy Maiga, Planeta, and vocalist Linda EPO, ensuring that every hour brings a distinct sonic dialogue to the urban grid.
+The Saturday experience reaches beyond static staging with the arrival of the official PVDFest Parade. Weaving through the downtown grid, the parade brings stilt walkers, percussion ensembles, brass players, and community art collectives directly into the crowds, eradicating the physical barrier between spectator and performer.
+Providence has earned its reputation as the "Creative Capital" through decades of deliberate investment in community-driven arts, independent design, and historic architecture. The city's intimate geography makes it uniquely suited for a multi-stage street festival. Unlike massive metropolitan centers where festival venues require extensive subway journeys, Providence's historic Downcity district remains extraordinarily compact. Eighteenth-century brick facades, Art Deco commercial buildings, and turn-of-the-century civic monuments sit within steps of one another, framing the festival with authentic New England character.
+Cultural heritage takes precedence across the festival grounds. A centerpiece of Saturday's schedule is the Harris Family Narragansett Dance Troupe, whose ancestral songs and ceremonial dances honor the indigenous people who have inhabited the Narragansett Bay basin for thousands of years. This focus on local heritage reflects a commitment to centering Rhode Island's living history alongside modern experimental art.
+The visual and performing arts programming reflects this intersection of subcultures. Along Mathewson Street, the Black Marketplace establishes a dedicated retail corridor for regional Black-owned businesses, artisan jewelers, independent fashion labels, and culinary creators. On nearby stages, AS220, the city's legendary unjuried and uncensored arts incubator, teams up with Rhode Island Fashion Week to present "DRIP", an avant-garde runway show that transforms the street into an open-air fashion gallery. Throughout the weekend, visitors encounter performances by Flamenco Rhode Island, high-energy choreographies from the Afro-Fusion Dancers, and dynamic demonstrations by the RI Kung Fu and Lion Dance Club.
+Public art installations further distinguish PVDFest from standard music gatherings. Visitors navigating Burnside Park and Kennedy Plaza will encounter interactive Art Piano installations, inviting anyone from conservatory students to curious children to sit down and play. Nearby, the AGONZA mural battle pits gifted urban muralists against each other in real-time creative competition, while artist Andy Grover coordinates LEGO Providence, inviting festivalgoers to reconstruct city landmarks out of thousands of interlocking bricks. In maker spaces dotted along the side streets, regional sculptors, ceramicists, and printmakers invite attendees to watch master crafters at work. Detailed visitor resources compiled by GoProvidence highlight how these artistic spaces integrate seamlessly into the surrounding historic retail core.
+Experiencing PVDFest like a seasoned local requires understanding the flow of downtown traffic, dining traditions, and neighborhood layouts:
+PVDFest serves an essential civic function that extends far beyond weekend entertainment. In an era when major music festivals charge exorbitant ticket prices and privatize public parks, Providence's steadfast commitment to an entirely free, open-access model defends the democratic nature of civic space. Every resident, regardless of economic background, enjoys equal access to world-class headliners, indigenous performances, and creative workshops.
+The festival also provides vital economic stimulus to downtown small businesses. Mathewson and Washington Streets contain dozens of family-owned independent restaurants, used bookshops, and vintage clothing boutiques. By drawing thousands of visitors directly past storefronts rather than cordoning people into an isolated commercial compound, PVDFest channels visitor spending directly into the pockets of local proprietors, sustaining Providence's unique culinary and retail identity.
+Environmental mindfulness remains central to festival operations. With thousands gathering across sensitive urban parklands like Burnside Park and near the banks of the Woonasquatucket and Providence Rivers, the city deploys specialized green teams and volunteer recycling crews to divert food waste and beverage containers away from waterways. Encouraging attendees to arrive via RIPTA buses and commuter rail cuts the vehicular emissions and traffic congestion that typically accompany major New England gatherings. By maintaining clean public parks and supporting neighborhood artisans, PVDFest models how an urban street festival can celebrate diverse global traditions while protecting the physical and cultural fabric of the host city.
+When is PVDFest 2026 and how much are admission tickets?
+PVDFest runs Friday, September 18 from 5pm to 10pm, and Saturday, September 19 from noon to 10pm. Admission is completely free, with no tickets or reservations required for any stage or art installation.
+How do I reach Downtown Providence without a car?
+Take Amtrak or MBTA commuter rail directly into Providence Station, located a five-minute walk north of Burnside Park. Regional travelers can also utilize RIPTA buses, which terminate directly at Kennedy Plaza.
+Where are the main festival stages and activities located?
+Events are spread across Burnside Park, Kennedy Plaza, the Providence Rink, Washington Street, Mathewson Street, and Snow Street throughout Downcity Providence.
+What signature musical performance should visitors not miss?
+Do not miss Saturday's headline set at 8:30pm on the Plaza Stage, featuring New Orleans bounce star Big Freedia performing alongside the Earl Bright &amp; Elevated Choir.
+In the heart of Rhode Island's capital, the city turns asphalt into art and invites the world to dance without boundaries.
+This article is for informational and educational purposes only. It does not constitute legal, financial, or professional advice. While we strive to provide accurate and up-to-date information, travel policies, regulations, and conditions change rapidly. Always verify information with official sources before making travel decisions. Nomad Lawyer makes no representations about the accuracy, reliability, completeness, or suitability of the information provided. Readers should consult qualified professionals for advice specific to their circumstances. The views expressed in this article are those of the author and do not necessarily reflect the views of Nomad Lawyer.
+Founder &amp; Lead Developer
+Full-stack developer with 11+ years of experience and a passionate traveller. Raushan built Nomad Lawyer from the ground up with a vision to create the best travel and law experience on the web.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:44:48</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Downtown Providence turns its historic core and civic plazas into an open-access cultural celebration during PVDFest 2026. While Rhode Island ranks as the smallest state in the American union, its capital city unleashes an outsized cultural celebration where historic red-brick thoroughfares transform into an entirely walkable, vehicle-free urban amphitheater without a single ticket gate.</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
         </is>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U23"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -2771,11 +2771,6 @@
           <t>2026-09-17 13:44:48</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
           <t>by San Antonio Living VIA Metropolitan Transit Whether you're heading to the airport, downtown, or the missions, the Rapid Green Line could eventually make the trip smoother. Corderro checked in with VIA officials to see where the project stands and what riders can expect once construction is complete.</t>
@@ -2875,11 +2870,6 @@
           <t>2026-09-17 13:44:48</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>Downtown Providence turns its historic core and civic plazas into an open-access cultural celebration during PVDFest 2026. While Rhode Island ranks as the smallest state in the American union, its capital city unleashes an outsized cultural celebration where historic red-brick thoroughfares transform into an entirely walkable, vehicle-free urban amphitheater without a single ticket gate.</t>
@@ -2894,6 +2884,174 @@
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Expedia News</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Expedia+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.travelagentcentral.com/your-business/expedia-taap-adds-tiqets-activities-uk-agency-beta</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Expedia, Expedia TAAP</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Expedia (Brand) | Expedia TAAP (Brand)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Expedia TAAP Adds Tiqets Activities in U.K. Agency Beta - Travel Agent Central</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Newsdesk</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Expedia Group is bringing tours and attractions into its travel agent platform, starting with a small group of agencies in the U.K.
+Select U.K. agencies using Expedia TAAP, the company’s Travel Agent Affiliate Program, can now book activities from Tiqets, the attractions and museum ticketing platform Expedia Group recently acquired. The beta organizes those activities so agents can find a fitting option quickly while building a trip, the company said Thursday. Expedia did not say when the feature will reach TAAP agencies in the U.S. or other markets.
+“It allows us to spend less time searching, more time focusing on travelers,” said Liam Brophy, commercial manager at beta partner Flights Guru.
+The company’s B2B arm is also extending its Rapid API, the technology that lets partners sell Expedia inventory on their own sites, beyond lodging. A new Rapid Activities API is in beta with select partners and gives them access to attractions, museums, tours, and experiences, including Tiqets inventory. General availability is planned for early 2027.
+Both launches feed Expedia’s push to keep an entire trip on one platform. The company’s own research found that 77% of travelers want to book their travel in one place, said Stephen Cheng, vice president of Expedia Group B2B.
+Peter Friend, CEO of beta partner Global Hotel Card, said the order in which travelers book is changing as well.
+“Activities aren’t an afterthought anymore,” Friend said. “Booking the activity is increasingly becoming the starting point, and then travelers book the flight and hotel around them.”
+Air France-KLM Submits Final Bid for TAP Air Portugal StakeMSC World Atlantic Floats Out Ahead of 2027 U.S. DebutFlightHub: U.S. Domestic Fares Up 49% as Long-Haul Gets CheaperAdvisors Lean Harder on the GDS, Amadeus Study Finds</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:37:34</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Expedia Group is bringing tours and attractions into its travel agent platform, starting with a small group of agencies in the U. Select U.</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Abhee, Mondee</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Downtown Travel News</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22Downtown+Travel%22+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://klin.com/2026/09/30/lincoln-urges-fans-to-allow-extra-time-for-downtown-travel/</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-09-30 19:17:34</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Downtown Travel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Downtown Travel (Brand)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Lincoln Urges Fans to Allow Extra Time for Downtown Travel - klin.com</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Johnnie Adcox</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Fans traveling to downtown Lincoln for football and volleyball events should allow an extra 30 minutes to an hour because of construction and increased traffic, city officials say. Lincoln Transportation and Utilities and Park &amp; Go issued the reminder Wednesday.
+Drivers are encouraged to check traffic conditions before leaving, follow traffic signs and directions, and watch for pedestrians and bicyclists near event venues. LTU says it monitors traffic throughout the day and coordinates with public safety officials and event partners to keep vehicles moving.
+City parking garages east of 10th Street offer several options for downtown visitors. Drivers can check availability and reserve prepaid parking through Park &amp; Go. On Husker football home game days, fans can also pay $15 for all-day parking at downtown meters using Zone 90 in the Passport Parking app.
+Downtown garage locations include:
+The city recommends the following routes into Lincoln:
+Drivers can check current traffic conditions through Nebraska 511 or Waze. The city also provided a downtown parking map to help visitors plan their trips.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:37:34</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Fans traveling to downtown Lincoln for football and volleyball events should allow an extra 30 minutes to an hour because of construction and increased traffic, city officials say. Lincoln Transportation and Utilities and Park &amp; Go issued the reminder Wednesday.</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
         </is>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -2950,11 +2950,6 @@
           <t>2026-10-01 15:37:34</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
           <t>Expedia Group is bringing tours and attractions into its travel agent platform, starting with a small group of agencies in the U. Select U.</t>
@@ -3033,11 +3028,6 @@
           <t>2026-10-01 15:37:34</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
           <t>Fans traveling to downtown Lincoln for football and volleyball events should allow an extra 30 minutes to an hour because of construction and increased traffic, city officials say. Lincoln Transportation and Utilities and Park &amp; Go issued the reminder Wednesday.</t>
@@ -3052,6 +3042,98 @@
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Expedia News</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=Expedia+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.travolution.com/news/travel-sectors/travel-agents/expedia-taap-launches-beta-rapid-activities-api-for-agencies/</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-02 15:36:47</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Expedia, Expedia TAAP</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Expedia (Brand) | Expedia TAAP (Brand)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Expedia TAAP launches beta Rapid Activities API for agencies - Travolution</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Travel Weekly Group Ltd</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted
+by Ronan Daniel
+on                                Oct 2nd, 2026 at 15:29
+Expedia Group’s B2B division has launched a beta version of a Rapid Activities API that integrates inventory from Tiqets, recently acquired by Expedia.
+The connection is designed for its Expedia Travel Agent Affiliate Program (TAAP), the group’s B2B programme for agencies.
+TAAP already introduced a back-office API in June; bringing activities into the mix expands the Rapid API ecosystem, which until now has focused on accommodation. The new tool promises tailored curation of activities directly within the TAAP interface.
+Expedia is positioning the move as a response to a trend which it says it has identified among travellers.
+“According to Expedia Group’s latest study on end-to-end trip planning, 77% of travellers want to book their entire trip on a single platform,” said Stephen Cheng, vice-president at Expedia Group B2B.
+“Extending our Rapid API ecosystem to activities gives our partners the products and tools they need to better meet the needs of travellers who want to book every element of their journey from one place.”
+That shift in emphasis also reflects how some travellers now build a trip around experiences rather than adding them last.
+“Until now, we thought travellers chose a destination first, then searched for flights and a hotel before perhaps considering an activity,” said Peter Friend, chief executive of Global Hotel Card.
+“Today we are convinced they prioritise the experience, and the order in which they book is changing. Activities are no longer a simple add-on.
+The activity booking is increasingly the starting point for travellers’ experience, with flights and hotels then booked around it.
+We want to offer our customers the best possible activities; so we’re honoured to be a beta partner for the Rapid Activities API launch.”
+The API is launching in beta, with a general rollout planned for early 2027.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:38:46</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Posted by Ronan Daniel on Oct 2nd, 2026 at 15:29 Expedia Group’s B2B division has launched a beta version of a Rapid Activities API that integrates inventory from Tiqets, recently acquired by Expedia. The connection is designed for its Expedia Travel Agent Affiliate Program (TAAP), the group’s B2B programme for agencies.</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Abhee, Mondee</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
         </is>
